--- a/docs/perechen-otchetov/obrazcy/ФО-54.xlsx
+++ b/docs/perechen-otchetov/obrazcy/ФО-54.xlsx
@@ -643,7 +643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K64"/>
+  <dimension ref="A1:K67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -801,32 +801,32 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D8" s="8" t="n"/>
       <c r="E8" s="9" t="n">
-        <v>3120.846865</v>
+        <v>3159.108306</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>1924.10346</v>
+        <v>1962.3649</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>1668.4375</v>
+        <v>1706.69894</v>
       </c>
       <c r="H8" s="9" t="n">
-        <v>1609.27083</v>
+        <v>1647.53227</v>
       </c>
       <c r="I8" s="9" t="n">
         <v>577.83263</v>
       </c>
       <c r="J8" s="10" t="n">
-        <v>83.637438</v>
+        <v>83.956469</v>
       </c>
       <c r="K8" s="10" t="n">
-        <v>53.46105</v>
+        <v>54.024705</v>
       </c>
     </row>
     <row r="9" ht="13" customHeight="1">
@@ -836,32 +836,32 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D9" s="13" t="n"/>
       <c r="E9" s="14" t="n">
-        <v>1850.850833</v>
+        <v>1889.112274</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>1246.38917</v>
+        <v>1284.65061</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>809.6875</v>
+        <v>847.94894</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>809.6875</v>
+        <v>847.94894</v>
       </c>
       <c r="I9" s="14" t="n">
         <v>449.70167</v>
       </c>
       <c r="J9" s="15" t="n">
-        <v>64.962655</v>
+        <v>66.006191</v>
       </c>
       <c r="K9" s="15" t="n">
-        <v>43.746772</v>
+        <v>44.886106</v>
       </c>
     </row>
     <row r="10" ht="13" customHeight="1">
@@ -878,7 +878,7 @@
       </c>
       <c r="D10" s="18" t="n"/>
       <c r="E10" s="19" t="n">
-        <v>1389.288333</v>
+        <v>1389.288334</v>
       </c>
       <c r="F10" s="19" t="n">
         <v>784.82667</v>
@@ -1491,23 +1491,23 @@
         </is>
       </c>
       <c r="B30" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30" s="17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" s="18" t="n"/>
       <c r="E30" s="19" t="n">
-        <v>461.5625</v>
+        <v>499.82394</v>
       </c>
       <c r="F30" s="19" t="n">
-        <v>461.5625</v>
+        <v>499.82394</v>
       </c>
       <c r="G30" s="19" t="n">
-        <v>461.5625</v>
+        <v>499.82394</v>
       </c>
       <c r="H30" s="19" t="n">
-        <v>461.5625</v>
+        <v>499.82394</v>
       </c>
       <c r="I30" s="19" t="n">
         <v>0</v>
@@ -1522,7 +1522,7 @@
     <row r="31" ht="13" customHeight="1">
       <c r="A31" s="21" t="inlineStr">
         <is>
-          <t>ОсОО «Кут-Мүлк»</t>
+          <t>ОсОО «Ала-Арча Энерго»</t>
         </is>
       </c>
       <c r="B31" s="22" t="n"/>
@@ -1531,16 +1531,16 @@
       </c>
       <c r="D31" s="24" t="n"/>
       <c r="E31" s="25" t="n">
-        <v>461.5625</v>
+        <v>38.26144</v>
       </c>
       <c r="F31" s="25" t="n">
-        <v>461.5625</v>
+        <v>38.26144</v>
       </c>
       <c r="G31" s="25" t="n">
-        <v>461.5625</v>
+        <v>38.26144</v>
       </c>
       <c r="H31" s="25" t="n">
-        <v>461.5625</v>
+        <v>38.26144</v>
       </c>
       <c r="I31" s="25" t="n">
         <v>0</v>
@@ -1555,23 +1555,23 @@
     <row r="32" ht="13" customHeight="1">
       <c r="A32" s="27" t="inlineStr">
         <is>
-          <t>№ 23-1/019 от 05.05.2023, USD</t>
+          <t>№ 21-9/040 от 20.09.2021, EUR</t>
         </is>
       </c>
       <c r="B32" s="28" t="n"/>
       <c r="C32" s="28" t="n"/>
       <c r="D32" s="29" t="n"/>
       <c r="E32" s="30" t="n">
-        <v>461.5625</v>
+        <v>38.26144</v>
       </c>
       <c r="F32" s="30" t="n">
-        <v>461.5625</v>
+        <v>38.26144</v>
       </c>
       <c r="G32" s="30" t="n">
-        <v>461.5625</v>
+        <v>38.26144</v>
       </c>
       <c r="H32" s="30" t="n">
-        <v>461.5625</v>
+        <v>38.26144</v>
       </c>
       <c r="I32" s="30" t="n">
         <v>0</v>
@@ -1586,23 +1586,23 @@
     <row r="33" ht="13" customHeight="1">
       <c r="A33" s="32" t="inlineStr">
         <is>
-          <t>в тыс. USD (курс 87,50000)</t>
+          <t>в тыс. EUR (курс 101,50000)</t>
         </is>
       </c>
       <c r="B33" s="33" t="n"/>
       <c r="C33" s="33" t="n"/>
       <c r="D33" s="34" t="n"/>
       <c r="E33" s="35" t="n">
-        <v>5.275</v>
+        <v>0.37696</v>
       </c>
       <c r="F33" s="35" t="n">
-        <v>5.275</v>
+        <v>0.37696</v>
       </c>
       <c r="G33" s="35" t="n">
-        <v>5.275</v>
+        <v>0.37696</v>
       </c>
       <c r="H33" s="35" t="n">
-        <v>5.275</v>
+        <v>0.37696</v>
       </c>
       <c r="I33" s="35" t="n">
         <v>0</v>
@@ -1611,424 +1611,416 @@
       <c r="K33" s="33" t="n"/>
     </row>
     <row r="34" ht="13" customHeight="1">
-      <c r="A34" s="11" t="inlineStr">
+      <c r="A34" s="21" t="inlineStr">
+        <is>
+          <t>ОсОО «Кут-Мүлк»</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="n"/>
+      <c r="C34" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="24" t="n"/>
+      <c r="E34" s="25" t="n">
+        <v>461.5625</v>
+      </c>
+      <c r="F34" s="25" t="n">
+        <v>461.5625</v>
+      </c>
+      <c r="G34" s="25" t="n">
+        <v>461.5625</v>
+      </c>
+      <c r="H34" s="25" t="n">
+        <v>461.5625</v>
+      </c>
+      <c r="I34" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="K34" s="26" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" ht="13" customHeight="1">
+      <c r="A35" s="27" t="inlineStr">
+        <is>
+          <t>№ 23-1/019 от 05.05.2023, USD</t>
+        </is>
+      </c>
+      <c r="B35" s="28" t="n"/>
+      <c r="C35" s="28" t="n"/>
+      <c r="D35" s="29" t="n"/>
+      <c r="E35" s="30" t="n">
+        <v>461.5625</v>
+      </c>
+      <c r="F35" s="30" t="n">
+        <v>461.5625</v>
+      </c>
+      <c r="G35" s="30" t="n">
+        <v>461.5625</v>
+      </c>
+      <c r="H35" s="30" t="n">
+        <v>461.5625</v>
+      </c>
+      <c r="I35" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="31" t="n">
+        <v>100</v>
+      </c>
+      <c r="K35" s="31" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" ht="13" customHeight="1">
+      <c r="A36" s="32" t="inlineStr">
+        <is>
+          <t>в тыс. USD (курс 87,50000)</t>
+        </is>
+      </c>
+      <c r="B36" s="33" t="n"/>
+      <c r="C36" s="33" t="n"/>
+      <c r="D36" s="34" t="n"/>
+      <c r="E36" s="35" t="n">
+        <v>5.275</v>
+      </c>
+      <c r="F36" s="35" t="n">
+        <v>5.275</v>
+      </c>
+      <c r="G36" s="35" t="n">
+        <v>5.275</v>
+      </c>
+      <c r="H36" s="35" t="n">
+        <v>5.275</v>
+      </c>
+      <c r="I36" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="33" t="n"/>
+      <c r="K36" s="33" t="n"/>
+    </row>
+    <row r="37" ht="13" customHeight="1">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t>Департамент регионального развития</t>
         </is>
       </c>
-      <c r="B34" s="12" t="n">
+      <c r="B37" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="C34" s="12" t="n">
+      <c r="C37" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="D34" s="13" t="n"/>
-      <c r="E34" s="14" t="n">
+      <c r="D37" s="13" t="n"/>
+      <c r="E37" s="14" t="n">
         <v>1269.996032</v>
       </c>
-      <c r="F34" s="14" t="n">
+      <c r="F37" s="14" t="n">
         <v>677.71429</v>
       </c>
-      <c r="G34" s="14" t="n">
+      <c r="G37" s="14" t="n">
         <v>858.75</v>
       </c>
-      <c r="H34" s="14" t="n">
+      <c r="H37" s="14" t="n">
         <v>799.58333</v>
       </c>
-      <c r="I34" s="14" t="n">
+      <c r="I37" s="14" t="n">
         <v>128.13096</v>
       </c>
-      <c r="J34" s="15" t="n">
+      <c r="J37" s="15" t="n">
         <v>117.982362</v>
       </c>
-      <c r="K34" s="15" t="n">
+      <c r="K37" s="15" t="n">
         <v>67.61832200000001</v>
       </c>
     </row>
-    <row r="35" ht="13" customHeight="1">
-      <c r="A35" s="16" t="inlineStr">
+    <row r="38" ht="13" customHeight="1">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>Жумабаев Р. С.</t>
         </is>
       </c>
-      <c r="B35" s="17" t="n">
+      <c r="B38" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="C35" s="17" t="n">
+      <c r="C38" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="D35" s="18" t="n"/>
-      <c r="E35" s="19" t="n">
-        <v>243.835314</v>
-      </c>
-      <c r="F35" s="19" t="n">
+      <c r="D38" s="18" t="n"/>
+      <c r="E38" s="19" t="n">
+        <v>243.835315</v>
+      </c>
+      <c r="F38" s="19" t="n">
         <v>95.75</v>
       </c>
-      <c r="G35" s="19" t="n">
+      <c r="G38" s="19" t="n">
         <v>72.08333</v>
       </c>
-      <c r="H35" s="19" t="n">
+      <c r="H38" s="19" t="n">
         <v>72.08333</v>
       </c>
-      <c r="I35" s="19" t="n">
+      <c r="I38" s="19" t="n">
         <v>23.66667</v>
       </c>
-      <c r="J35" s="20" t="n">
+      <c r="J38" s="20" t="n">
         <v>75.28285099999999</v>
       </c>
-      <c r="K35" s="20" t="n">
+      <c r="K38" s="20" t="n">
         <v>29.562301</v>
       </c>
     </row>
-    <row r="36" ht="13" customHeight="1">
-      <c r="A36" s="21" t="inlineStr">
+    <row r="39" ht="13" customHeight="1">
+      <c r="A39" s="21" t="inlineStr">
         <is>
           <t>КФХ «Ак-Суу»</t>
         </is>
       </c>
-      <c r="B36" s="22" t="n"/>
-      <c r="C36" s="23" t="n">
+      <c r="B39" s="22" t="n"/>
+      <c r="C39" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D36" s="24" t="n"/>
-      <c r="E36" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="25" t="n">
+      <c r="D39" s="24" t="n"/>
+      <c r="E39" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="25" t="n">
         <v>18.4</v>
       </c>
-      <c r="G36" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="25" t="n">
+      <c r="G39" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="25" t="n">
         <v>18.4</v>
       </c>
-      <c r="J36" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" s="22" t="n"/>
-    </row>
-    <row r="37" ht="13" customHeight="1">
-      <c r="A37" s="27" t="inlineStr">
+      <c r="J39" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="22" t="n"/>
+    </row>
+    <row r="40" ht="13" customHeight="1">
+      <c r="A40" s="27" t="inlineStr">
         <is>
           <t>№ 20-6/027 от 12.05.2020, KGS</t>
         </is>
       </c>
-      <c r="B37" s="28" t="n"/>
-      <c r="C37" s="28" t="n"/>
-      <c r="D37" s="36" t="n">
+      <c r="B40" s="28" t="n"/>
+      <c r="C40" s="28" t="n"/>
+      <c r="D40" s="36" t="n">
         <v>46254</v>
       </c>
-      <c r="E37" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="30" t="n">
+      <c r="E40" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="30" t="n">
         <v>18.4</v>
       </c>
-      <c r="G37" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" s="30" t="n">
+      <c r="G40" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="30" t="n">
         <v>18.4</v>
       </c>
-      <c r="J37" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" s="28" t="n"/>
-    </row>
-    <row r="38" ht="13" customHeight="1">
-      <c r="A38" s="21" t="inlineStr">
+      <c r="J40" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="28" t="n"/>
+    </row>
+    <row r="41" ht="13" customHeight="1">
+      <c r="A41" s="21" t="inlineStr">
         <is>
           <t>Иманалиев Бакыт Тологонович</t>
         </is>
       </c>
-      <c r="B38" s="22" t="n"/>
-      <c r="C38" s="23" t="n">
+      <c r="B41" s="22" t="n"/>
+      <c r="C41" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D38" s="24" t="n"/>
-      <c r="E38" s="25" t="n">
+      <c r="D41" s="24" t="n"/>
+      <c r="E41" s="25" t="n">
         <v>12.625</v>
       </c>
-      <c r="F38" s="25" t="n">
+      <c r="F41" s="25" t="n">
         <v>5.26667</v>
       </c>
-      <c r="G38" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="25" t="n">
+      <c r="G41" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="25" t="n">
         <v>5.26667</v>
       </c>
-      <c r="J38" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" s="26" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" ht="13" customHeight="1">
-      <c r="A39" s="27" t="inlineStr">
+      <c r="J41" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" ht="13" customHeight="1">
+      <c r="A42" s="27" t="inlineStr">
         <is>
           <t>№ 24-2/077 от 14.05.2024, KGS</t>
         </is>
       </c>
-      <c r="B39" s="28" t="n"/>
-      <c r="C39" s="28" t="n"/>
-      <c r="D39" s="29" t="n"/>
-      <c r="E39" s="30" t="n">
+      <c r="B42" s="28" t="n"/>
+      <c r="C42" s="28" t="n"/>
+      <c r="D42" s="29" t="n"/>
+      <c r="E42" s="30" t="n">
         <v>12.625</v>
       </c>
-      <c r="F39" s="30" t="n">
+      <c r="F42" s="30" t="n">
         <v>5.26667</v>
       </c>
-      <c r="G39" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="30" t="n">
+      <c r="G42" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="30" t="n">
         <v>5.26667</v>
       </c>
-      <c r="J39" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" s="31" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" ht="13" customHeight="1">
-      <c r="A40" s="21" t="inlineStr">
+      <c r="J42" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" ht="13" customHeight="1">
+      <c r="A43" s="21" t="inlineStr">
         <is>
           <t>ОсОО «Нарын-Агро»</t>
         </is>
       </c>
-      <c r="B40" s="22" t="n"/>
-      <c r="C40" s="23" t="n">
+      <c r="B43" s="22" t="n"/>
+      <c r="C43" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D40" s="24" t="n"/>
-      <c r="E40" s="25" t="n">
+      <c r="D43" s="24" t="n"/>
+      <c r="E43" s="25" t="n">
         <v>68.57142899999999</v>
       </c>
-      <c r="F40" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="22" t="n"/>
-      <c r="K40" s="26" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" ht="13" customHeight="1">
-      <c r="A41" s="27" t="inlineStr">
+      <c r="F43" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" s="22" t="n"/>
+      <c r="K43" s="26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" ht="13" customHeight="1">
+      <c r="A44" s="27" t="inlineStr">
         <is>
           <t>№ 21-2/077 от 18.05.2021, KGS</t>
         </is>
       </c>
-      <c r="B41" s="28" t="n"/>
-      <c r="C41" s="28" t="n"/>
-      <c r="D41" s="29" t="n"/>
-      <c r="E41" s="30" t="n">
+      <c r="B44" s="28" t="n"/>
+      <c r="C44" s="28" t="n"/>
+      <c r="D44" s="29" t="n"/>
+      <c r="E44" s="30" t="n">
         <v>68.57142899999999</v>
       </c>
-      <c r="F41" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="28" t="n"/>
-      <c r="K41" s="31" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" ht="13" customHeight="1">
-      <c r="A42" s="21" t="inlineStr">
+      <c r="F44" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="28" t="n"/>
+      <c r="K44" s="31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" ht="13" customHeight="1">
+      <c r="A45" s="21" t="inlineStr">
         <is>
           <t>ОсОО «Талас-Бал»</t>
         </is>
       </c>
-      <c r="B42" s="22" t="n"/>
-      <c r="C42" s="23" t="n">
+      <c r="B45" s="22" t="n"/>
+      <c r="C45" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D42" s="24" t="n"/>
-      <c r="E42" s="25" t="n">
+      <c r="D45" s="24" t="n"/>
+      <c r="E45" s="25" t="n">
         <v>90.555556</v>
       </c>
-      <c r="F42" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="22" t="n"/>
-      <c r="K42" s="26" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" ht="13" customHeight="1">
-      <c r="A43" s="27" t="inlineStr">
+      <c r="F45" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="22" t="n"/>
+      <c r="K45" s="26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" ht="13" customHeight="1">
+      <c r="A46" s="27" t="inlineStr">
         <is>
           <t>№ 23-4/021 от 21.08.2023, KGS</t>
         </is>
       </c>
-      <c r="B43" s="28" t="n"/>
-      <c r="C43" s="28" t="n"/>
-      <c r="D43" s="29" t="n"/>
-      <c r="E43" s="30" t="n">
+      <c r="B46" s="28" t="n"/>
+      <c r="C46" s="28" t="n"/>
+      <c r="D46" s="29" t="n"/>
+      <c r="E46" s="30" t="n">
         <v>90.555556</v>
       </c>
-      <c r="F43" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="28" t="n"/>
-      <c r="K43" s="31" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" ht="13" customHeight="1">
-      <c r="A44" s="21" t="inlineStr">
-        <is>
-          <t>ОсОО «Ысык-Көл Логистик»</t>
-        </is>
-      </c>
-      <c r="B44" s="22" t="n"/>
-      <c r="C44" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D44" s="24" t="n"/>
-      <c r="E44" s="25" t="n">
-        <v>72.08333</v>
-      </c>
-      <c r="F44" s="25" t="n">
-        <v>72.08333</v>
-      </c>
-      <c r="G44" s="25" t="n">
-        <v>72.08333</v>
-      </c>
-      <c r="H44" s="25" t="n">
-        <v>72.08333</v>
-      </c>
-      <c r="I44" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="K44" s="26" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="45" ht="13" customHeight="1">
-      <c r="A45" s="27" t="inlineStr">
-        <is>
-          <t>№ 21-6/144 от 02.06.2021, KGS</t>
-        </is>
-      </c>
-      <c r="B45" s="28" t="n"/>
-      <c r="C45" s="28" t="n"/>
-      <c r="D45" s="29" t="n"/>
-      <c r="E45" s="30" t="n">
-        <v>72.08333</v>
-      </c>
-      <c r="F45" s="30" t="n">
-        <v>72.08333</v>
-      </c>
-      <c r="G45" s="30" t="n">
-        <v>72.08333</v>
-      </c>
-      <c r="H45" s="30" t="n">
-        <v>72.08333</v>
-      </c>
-      <c r="I45" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="31" t="n">
-        <v>100</v>
-      </c>
-      <c r="K45" s="31" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="46" ht="13" customHeight="1">
-      <c r="A46" s="16" t="inlineStr">
-        <is>
-          <t>Осмонов Б. Т.</t>
-        </is>
-      </c>
-      <c r="B46" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="C46" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="D46" s="18" t="n"/>
-      <c r="E46" s="19" t="n">
-        <v>776.458333</v>
-      </c>
-      <c r="F46" s="19" t="n">
-        <v>465.71429</v>
-      </c>
-      <c r="G46" s="19" t="n">
-        <v>611.25</v>
-      </c>
-      <c r="H46" s="19" t="n">
-        <v>611.25</v>
-      </c>
-      <c r="I46" s="19" t="n">
-        <v>104.46429</v>
-      </c>
-      <c r="J46" s="20" t="n">
-        <v>131.249999</v>
-      </c>
-      <c r="K46" s="20" t="n">
-        <v>78.72283299999999</v>
+      <c r="F46" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="28" t="n"/>
+      <c r="K46" s="31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47" ht="13" customHeight="1">
       <c r="A47" s="21" t="inlineStr">
         <is>
-          <t>ОсОО «Ош-Текстиль»</t>
+          <t>ОсОО «Ысык-Көл Логистик»</t>
         </is>
       </c>
       <c r="B47" s="22" t="n"/>
@@ -2037,279 +2029,289 @@
       </c>
       <c r="D47" s="24" t="n"/>
       <c r="E47" s="25" t="n">
-        <v>230</v>
+        <v>72.08333</v>
       </c>
       <c r="F47" s="25" t="n">
-        <v>104.46429</v>
+        <v>72.08333</v>
       </c>
       <c r="G47" s="25" t="n">
-        <v>0</v>
+        <v>72.08333</v>
       </c>
       <c r="H47" s="25" t="n">
-        <v>0</v>
+        <v>72.08333</v>
       </c>
       <c r="I47" s="25" t="n">
-        <v>104.46429</v>
+        <v>0</v>
       </c>
       <c r="J47" s="26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K47" s="26" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48" ht="13" customHeight="1">
       <c r="A48" s="27" t="inlineStr">
         <is>
-          <t>№ 21-5/203 от 09.09.2021, KGS</t>
+          <t>№ 21-6/144 от 02.06.2021, KGS</t>
         </is>
       </c>
       <c r="B48" s="28" t="n"/>
       <c r="C48" s="28" t="n"/>
       <c r="D48" s="29" t="n"/>
       <c r="E48" s="30" t="n">
+        <v>72.08333</v>
+      </c>
+      <c r="F48" s="30" t="n">
+        <v>72.08333</v>
+      </c>
+      <c r="G48" s="30" t="n">
+        <v>72.08333</v>
+      </c>
+      <c r="H48" s="30" t="n">
+        <v>72.08333</v>
+      </c>
+      <c r="I48" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" s="31" t="n">
+        <v>100</v>
+      </c>
+      <c r="K48" s="31" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" ht="13" customHeight="1">
+      <c r="A49" s="16" t="inlineStr">
+        <is>
+          <t>Осмонов Б. Т.</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C49" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="D49" s="18" t="n"/>
+      <c r="E49" s="19" t="n">
+        <v>776.458333</v>
+      </c>
+      <c r="F49" s="19" t="n">
+        <v>465.71429</v>
+      </c>
+      <c r="G49" s="19" t="n">
+        <v>611.25</v>
+      </c>
+      <c r="H49" s="19" t="n">
+        <v>611.25</v>
+      </c>
+      <c r="I49" s="19" t="n">
+        <v>104.46429</v>
+      </c>
+      <c r="J49" s="20" t="n">
+        <v>131.249999</v>
+      </c>
+      <c r="K49" s="20" t="n">
+        <v>78.72283299999999</v>
+      </c>
+    </row>
+    <row r="50" ht="13" customHeight="1">
+      <c r="A50" s="21" t="inlineStr">
+        <is>
+          <t>ОсОО «Ош-Текстиль»</t>
+        </is>
+      </c>
+      <c r="B50" s="22" t="n"/>
+      <c r="C50" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" s="24" t="n"/>
+      <c r="E50" s="25" t="n">
         <v>230</v>
       </c>
-      <c r="F48" s="30" t="n">
+      <c r="F50" s="25" t="n">
         <v>104.46429</v>
       </c>
-      <c r="G48" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" s="30" t="n">
+      <c r="G50" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="25" t="n">
         <v>104.46429</v>
       </c>
-      <c r="J48" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" s="31" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" ht="13" customHeight="1">
-      <c r="A49" s="21" t="inlineStr">
+      <c r="J50" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" ht="13" customHeight="1">
+      <c r="A51" s="27" t="inlineStr">
+        <is>
+          <t>№ 21-5/203 от 09.09.2021, KGS</t>
+        </is>
+      </c>
+      <c r="B51" s="28" t="n"/>
+      <c r="C51" s="28" t="n"/>
+      <c r="D51" s="29" t="n"/>
+      <c r="E51" s="30" t="n">
+        <v>230</v>
+      </c>
+      <c r="F51" s="30" t="n">
+        <v>104.46429</v>
+      </c>
+      <c r="G51" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="30" t="n">
+        <v>104.46429</v>
+      </c>
+      <c r="J51" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" ht="13" customHeight="1">
+      <c r="A52" s="21" t="inlineStr">
         <is>
           <t>ОсОО «Ак-Булак»</t>
         </is>
       </c>
-      <c r="B49" s="22" t="n"/>
-      <c r="C49" s="23" t="n">
+      <c r="B52" s="22" t="n"/>
+      <c r="C52" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D49" s="24" t="n"/>
-      <c r="E49" s="25" t="n">
+      <c r="D52" s="24" t="n"/>
+      <c r="E52" s="25" t="n">
         <v>74.58333</v>
       </c>
-      <c r="F49" s="25" t="n">
+      <c r="F52" s="25" t="n">
         <v>74.58333</v>
       </c>
-      <c r="G49" s="25" t="n">
+      <c r="G52" s="25" t="n">
         <v>74.58333</v>
       </c>
-      <c r="H49" s="25" t="n">
+      <c r="H52" s="25" t="n">
         <v>74.58333</v>
       </c>
-      <c r="I49" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="K49" s="26" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="50" ht="13" customHeight="1">
-      <c r="A50" s="27" t="inlineStr">
+      <c r="I52" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="K52" s="26" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" ht="13" customHeight="1">
+      <c r="A53" s="27" t="inlineStr">
         <is>
           <t>№ 24-6/019 от 11.02.2024, KGS</t>
         </is>
       </c>
-      <c r="B50" s="28" t="n"/>
-      <c r="C50" s="28" t="n"/>
-      <c r="D50" s="29" t="n"/>
-      <c r="E50" s="30" t="n">
+      <c r="B53" s="28" t="n"/>
+      <c r="C53" s="28" t="n"/>
+      <c r="D53" s="29" t="n"/>
+      <c r="E53" s="30" t="n">
         <v>74.58333</v>
       </c>
-      <c r="F50" s="30" t="n">
+      <c r="F53" s="30" t="n">
         <v>74.58333</v>
       </c>
-      <c r="G50" s="30" t="n">
+      <c r="G53" s="30" t="n">
         <v>74.58333</v>
       </c>
-      <c r="H50" s="30" t="n">
+      <c r="H53" s="30" t="n">
         <v>74.58333</v>
       </c>
-      <c r="I50" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="31" t="n">
-        <v>100</v>
-      </c>
-      <c r="K50" s="31" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="51" ht="13" customHeight="1">
-      <c r="A51" s="21" t="inlineStr">
+      <c r="I53" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="31" t="n">
+        <v>100</v>
+      </c>
+      <c r="K53" s="31" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="54" ht="13" customHeight="1">
+      <c r="A54" s="21" t="inlineStr">
         <is>
           <t>ОсОО «Алтын-Тоо»</t>
         </is>
       </c>
-      <c r="B51" s="22" t="n"/>
-      <c r="C51" s="23" t="n">
+      <c r="B54" s="22" t="n"/>
+      <c r="C54" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D51" s="24" t="n"/>
-      <c r="E51" s="25" t="n">
+      <c r="D54" s="24" t="n"/>
+      <c r="E54" s="25" t="n">
         <v>16.66667</v>
       </c>
-      <c r="F51" s="25" t="n">
+      <c r="F54" s="25" t="n">
         <v>16.66667</v>
       </c>
-      <c r="G51" s="25" t="n">
+      <c r="G54" s="25" t="n">
         <v>16.66667</v>
       </c>
-      <c r="H51" s="25" t="n">
+      <c r="H54" s="25" t="n">
         <v>16.66667</v>
       </c>
-      <c r="I51" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="K51" s="26" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="52" ht="13" customHeight="1">
-      <c r="A52" s="27" t="inlineStr">
+      <c r="I54" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="K54" s="26" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55" ht="13" customHeight="1">
+      <c r="A55" s="27" t="inlineStr">
         <is>
           <t>№ 24-2/088 от 12.03.2024, KGS</t>
         </is>
       </c>
-      <c r="B52" s="28" t="n"/>
-      <c r="C52" s="28" t="n"/>
-      <c r="D52" s="29" t="n"/>
-      <c r="E52" s="30" t="n">
+      <c r="B55" s="28" t="n"/>
+      <c r="C55" s="28" t="n"/>
+      <c r="D55" s="29" t="n"/>
+      <c r="E55" s="30" t="n">
         <v>16.66667</v>
       </c>
-      <c r="F52" s="30" t="n">
+      <c r="F55" s="30" t="n">
         <v>16.66667</v>
       </c>
-      <c r="G52" s="30" t="n">
+      <c r="G55" s="30" t="n">
         <v>16.66667</v>
       </c>
-      <c r="H52" s="30" t="n">
+      <c r="H55" s="30" t="n">
         <v>16.66667</v>
       </c>
-      <c r="I52" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="31" t="n">
-        <v>100</v>
-      </c>
-      <c r="K52" s="31" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="53" ht="13" customHeight="1">
-      <c r="A53" s="21" t="inlineStr">
-        <is>
-          <t>ОсОО «Кербен-Жибек»</t>
-        </is>
-      </c>
-      <c r="B53" s="22" t="n"/>
-      <c r="C53" s="23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D53" s="24" t="n"/>
-      <c r="E53" s="25" t="n">
-        <v>185.208333</v>
-      </c>
-      <c r="F53" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" s="22" t="n"/>
-      <c r="K53" s="26" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" ht="13" customHeight="1">
-      <c r="A54" s="27" t="inlineStr">
-        <is>
-          <t>№ 20-5/118 от 23.06.2020, USD</t>
-        </is>
-      </c>
-      <c r="B54" s="28" t="n"/>
-      <c r="C54" s="28" t="n"/>
-      <c r="D54" s="36" t="n">
-        <v>46269</v>
-      </c>
-      <c r="E54" s="30" t="n">
-        <v>185.208333</v>
-      </c>
-      <c r="F54" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="28" t="n"/>
-      <c r="K54" s="31" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" ht="13" customHeight="1">
-      <c r="A55" s="32" t="inlineStr">
-        <is>
-          <t>в тыс. USD (курс 87,50000)</t>
-        </is>
-      </c>
-      <c r="B55" s="33" t="n"/>
-      <c r="C55" s="33" t="n"/>
-      <c r="D55" s="34" t="n"/>
-      <c r="E55" s="35" t="n">
-        <v>2.116667</v>
-      </c>
-      <c r="F55" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="33" t="n"/>
-      <c r="K55" s="33" t="n"/>
+      <c r="I55" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="31" t="n">
+        <v>100</v>
+      </c>
+      <c r="K55" s="31" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="56" ht="13" customHeight="1">
       <c r="A56" s="21" t="inlineStr">
         <is>
-          <t>ОсОО «Ош-Нан»</t>
+          <t>ОсОО «Кербен-Жибек»</t>
         </is>
       </c>
       <c r="B56" s="22" t="n"/>
@@ -2318,97 +2320,87 @@
       </c>
       <c r="D56" s="24" t="n"/>
       <c r="E56" s="25" t="n">
-        <v>270</v>
+        <v>185.208333</v>
       </c>
       <c r="F56" s="25" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="G56" s="25" t="n">
-        <v>520</v>
+        <v>0</v>
       </c>
       <c r="H56" s="25" t="n">
-        <v>520</v>
+        <v>0</v>
       </c>
       <c r="I56" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="J56" s="26" t="n">
-        <v>192.592593</v>
-      </c>
+      <c r="J56" s="22" t="n"/>
       <c r="K56" s="26" t="n">
-        <v>192.592593</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" ht="13" customHeight="1">
       <c r="A57" s="27" t="inlineStr">
         <is>
-          <t>№ 20-1/412 от 14.10.2020, KGS</t>
+          <t>№ 20-5/118 от 23.06.2020, USD</t>
         </is>
       </c>
       <c r="B57" s="28" t="n"/>
       <c r="C57" s="28" t="n"/>
-      <c r="D57" s="29" t="n"/>
+      <c r="D57" s="36" t="n">
+        <v>46269</v>
+      </c>
       <c r="E57" s="30" t="n">
-        <v>270</v>
+        <v>185.208333</v>
       </c>
       <c r="F57" s="30" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="G57" s="30" t="n">
-        <v>520</v>
+        <v>0</v>
       </c>
       <c r="H57" s="30" t="n">
-        <v>520</v>
+        <v>0</v>
       </c>
       <c r="I57" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="J57" s="31" t="n">
-        <v>192.592593</v>
-      </c>
+      <c r="J57" s="28" t="n"/>
       <c r="K57" s="31" t="n">
-        <v>192.592593</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" ht="13" customHeight="1">
-      <c r="A58" s="16" t="inlineStr">
-        <is>
-          <t>Токтогулова Г. А.</t>
-        </is>
-      </c>
-      <c r="B58" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="C58" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="D58" s="18" t="n"/>
-      <c r="E58" s="19" t="n">
-        <v>249.702384</v>
-      </c>
-      <c r="F58" s="19" t="n">
-        <v>116.25</v>
-      </c>
-      <c r="G58" s="19" t="n">
-        <v>175.41667</v>
-      </c>
-      <c r="H58" s="19" t="n">
-        <v>116.25</v>
-      </c>
-      <c r="I58" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="20" t="n">
-        <v>100</v>
-      </c>
-      <c r="K58" s="20" t="n">
-        <v>70.250298</v>
-      </c>
+      <c r="A58" s="32" t="inlineStr">
+        <is>
+          <t>в тыс. USD (курс 87,50000)</t>
+        </is>
+      </c>
+      <c r="B58" s="33" t="n"/>
+      <c r="C58" s="33" t="n"/>
+      <c r="D58" s="34" t="n"/>
+      <c r="E58" s="35" t="n">
+        <v>2.116667</v>
+      </c>
+      <c r="F58" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="33" t="n"/>
+      <c r="K58" s="33" t="n"/>
     </row>
     <row r="59" ht="13" customHeight="1">
       <c r="A59" s="21" t="inlineStr">
         <is>
-          <t>ОсОО «Ала-Тоо Агро»</t>
+          <t>ОсОО «Ош-Нан»</t>
         </is>
       </c>
       <c r="B59" s="22" t="n"/>
@@ -2417,163 +2409,262 @@
       </c>
       <c r="D59" s="24" t="n"/>
       <c r="E59" s="25" t="n">
-        <v>116.25</v>
+        <v>270</v>
       </c>
       <c r="F59" s="25" t="n">
-        <v>116.25</v>
+        <v>270</v>
       </c>
       <c r="G59" s="25" t="n">
-        <v>116.25</v>
+        <v>520</v>
       </c>
       <c r="H59" s="25" t="n">
-        <v>116.25</v>
+        <v>520</v>
       </c>
       <c r="I59" s="25" t="n">
         <v>0</v>
       </c>
       <c r="J59" s="26" t="n">
-        <v>100</v>
+        <v>192.592593</v>
       </c>
       <c r="K59" s="26" t="n">
-        <v>100</v>
+        <v>192.592593</v>
       </c>
     </row>
     <row r="60" ht="13" customHeight="1">
       <c r="A60" s="27" t="inlineStr">
         <is>
-          <t>№ 25-4/030 от 10.02.2025, KGS</t>
+          <t>№ 20-1/412 от 14.10.2020, KGS</t>
         </is>
       </c>
       <c r="B60" s="28" t="n"/>
       <c r="C60" s="28" t="n"/>
       <c r="D60" s="29" t="n"/>
       <c r="E60" s="30" t="n">
+        <v>270</v>
+      </c>
+      <c r="F60" s="30" t="n">
+        <v>270</v>
+      </c>
+      <c r="G60" s="30" t="n">
+        <v>520</v>
+      </c>
+      <c r="H60" s="30" t="n">
+        <v>520</v>
+      </c>
+      <c r="I60" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="31" t="n">
+        <v>192.592593</v>
+      </c>
+      <c r="K60" s="31" t="n">
+        <v>192.592593</v>
+      </c>
+    </row>
+    <row r="61" ht="13" customHeight="1">
+      <c r="A61" s="16" t="inlineStr">
+        <is>
+          <t>Токтогулова Г. А.</t>
+        </is>
+      </c>
+      <c r="B61" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C61" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D61" s="18" t="n"/>
+      <c r="E61" s="19" t="n">
+        <v>249.702384</v>
+      </c>
+      <c r="F61" s="19" t="n">
         <v>116.25</v>
       </c>
-      <c r="F60" s="30" t="n">
+      <c r="G61" s="19" t="n">
+        <v>175.41667</v>
+      </c>
+      <c r="H61" s="19" t="n">
         <v>116.25</v>
       </c>
-      <c r="G60" s="30" t="n">
+      <c r="I61" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="20" t="n">
+        <v>100</v>
+      </c>
+      <c r="K61" s="20" t="n">
+        <v>70.250298</v>
+      </c>
+    </row>
+    <row r="62" ht="13" customHeight="1">
+      <c r="A62" s="21" t="inlineStr">
+        <is>
+          <t>ОсОО «Ала-Тоо Агро»</t>
+        </is>
+      </c>
+      <c r="B62" s="22" t="n"/>
+      <c r="C62" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" s="24" t="n"/>
+      <c r="E62" s="25" t="n">
         <v>116.25</v>
       </c>
-      <c r="H60" s="30" t="n">
+      <c r="F62" s="25" t="n">
         <v>116.25</v>
       </c>
-      <c r="I60" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="31" t="n">
-        <v>100</v>
-      </c>
-      <c r="K60" s="31" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="61" ht="13" customHeight="1">
-      <c r="A61" s="21" t="inlineStr">
+      <c r="G62" s="25" t="n">
+        <v>116.25</v>
+      </c>
+      <c r="H62" s="25" t="n">
+        <v>116.25</v>
+      </c>
+      <c r="I62" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="K62" s="26" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="63" ht="13" customHeight="1">
+      <c r="A63" s="27" t="inlineStr">
+        <is>
+          <t>№ 25-4/030 от 10.02.2025, KGS</t>
+        </is>
+      </c>
+      <c r="B63" s="28" t="n"/>
+      <c r="C63" s="28" t="n"/>
+      <c r="D63" s="29" t="n"/>
+      <c r="E63" s="30" t="n">
+        <v>116.25</v>
+      </c>
+      <c r="F63" s="30" t="n">
+        <v>116.25</v>
+      </c>
+      <c r="G63" s="30" t="n">
+        <v>116.25</v>
+      </c>
+      <c r="H63" s="30" t="n">
+        <v>116.25</v>
+      </c>
+      <c r="I63" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="31" t="n">
+        <v>100</v>
+      </c>
+      <c r="K63" s="31" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="64" ht="13" customHeight="1">
+      <c r="A64" s="21" t="inlineStr">
         <is>
           <t>ОсОО «Каракол-Сервис»</t>
         </is>
       </c>
-      <c r="B61" s="22" t="n"/>
-      <c r="C61" s="23" t="n">
+      <c r="B64" s="22" t="n"/>
+      <c r="C64" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D61" s="24" t="n"/>
-      <c r="E61" s="25" t="n">
+      <c r="D64" s="24" t="n"/>
+      <c r="E64" s="25" t="n">
         <v>59.16667</v>
       </c>
-      <c r="F61" s="22" t="n"/>
-      <c r="G61" s="25" t="n">
+      <c r="F64" s="22" t="n"/>
+      <c r="G64" s="25" t="n">
         <v>59.16667</v>
       </c>
-      <c r="H61" s="22" t="n"/>
-      <c r="I61" s="22" t="n"/>
-      <c r="J61" s="22" t="n"/>
-      <c r="K61" s="26" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="62" ht="13" customHeight="1">
-      <c r="A62" s="27" t="inlineStr">
+      <c r="H64" s="22" t="n"/>
+      <c r="I64" s="22" t="n"/>
+      <c r="J64" s="22" t="n"/>
+      <c r="K64" s="26" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="65" ht="13" customHeight="1">
+      <c r="A65" s="27" t="inlineStr">
         <is>
           <t>№ 25-3/014 от 05.03.2025, KGS</t>
         </is>
       </c>
-      <c r="B62" s="28" t="n"/>
-      <c r="C62" s="28" t="n"/>
-      <c r="D62" s="29" t="n"/>
-      <c r="E62" s="30" t="n">
+      <c r="B65" s="28" t="n"/>
+      <c r="C65" s="28" t="n"/>
+      <c r="D65" s="29" t="n"/>
+      <c r="E65" s="30" t="n">
         <v>59.16667</v>
       </c>
-      <c r="F62" s="28" t="n"/>
-      <c r="G62" s="30" t="n">
+      <c r="F65" s="28" t="n"/>
+      <c r="G65" s="30" t="n">
         <v>59.16667</v>
       </c>
-      <c r="H62" s="28" t="n"/>
-      <c r="I62" s="28" t="n"/>
-      <c r="J62" s="28" t="n"/>
-      <c r="K62" s="31" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="63" ht="13" customHeight="1">
-      <c r="A63" s="21" t="inlineStr">
+      <c r="H65" s="28" t="n"/>
+      <c r="I65" s="28" t="n"/>
+      <c r="J65" s="28" t="n"/>
+      <c r="K65" s="31" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="66" ht="13" customHeight="1">
+      <c r="A66" s="21" t="inlineStr">
         <is>
           <t>ОсОО «Нарын-Сүт»</t>
         </is>
       </c>
-      <c r="B63" s="22" t="n"/>
-      <c r="C63" s="23" t="n">
+      <c r="B66" s="22" t="n"/>
+      <c r="C66" s="23" t="n">
         <v>1</v>
       </c>
-      <c r="D63" s="24" t="n"/>
-      <c r="E63" s="25" t="n">
+      <c r="D66" s="24" t="n"/>
+      <c r="E66" s="25" t="n">
         <v>74.285714</v>
       </c>
-      <c r="F63" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="22" t="n"/>
-      <c r="K63" s="26" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" ht="13" customHeight="1">
-      <c r="A64" s="27" t="inlineStr">
+      <c r="F66" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="22" t="n"/>
+      <c r="K66" s="26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" ht="13" customHeight="1">
+      <c r="A67" s="27" t="inlineStr">
         <is>
           <t>№ 23-5/071 от 09.08.2023, KGS</t>
         </is>
       </c>
-      <c r="B64" s="28" t="n"/>
-      <c r="C64" s="28" t="n"/>
-      <c r="D64" s="29" t="n"/>
-      <c r="E64" s="30" t="n">
+      <c r="B67" s="28" t="n"/>
+      <c r="C67" s="28" t="n"/>
+      <c r="D67" s="29" t="n"/>
+      <c r="E67" s="30" t="n">
         <v>74.285714</v>
       </c>
-      <c r="F64" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" s="28" t="n"/>
-      <c r="K64" s="31" t="n">
+      <c r="F67" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="28" t="n"/>
+      <c r="K67" s="31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3194,7 +3285,7 @@
       </c>
       <c r="B35" s="42" t="inlineStr">
         <is>
-          <t>Сентябрь 2026, план на 06.10.2026: 21 заёмщик, 24 кредита; по графику 3 120,847 тыс. сом, по плану 1 924,103, погашено 1 668,438, в месяцы с планом 1 609,271; недобор к плану 577,833; исполнение плана 83,6 %; погашено к графику 53,5 %.</t>
+          <t>Сентябрь 2026, план на 06.10.2026: 22 заёмщика, 25 кредитов; по графику 3 159,108 тыс. сом, по плану 1 962,365, погашено 1 706,699, в месяцы с планом 1 647,532; недобор к плану 577,833; исполнение плана 84,0 %; погашено к графику 54,0 %.</t>
         </is>
       </c>
     </row>
@@ -3206,11 +3297,11 @@
       </c>
       <c r="B36" s="42" t="inlineStr">
         <is>
-          <t>«По плану за период» каждого кредита = план сентября в ФО-06 (план на 01.10.2026, правок плана сентября после 30.09.2026 нет); ИТОГО 1 924,103 = сентябрь ИТОГО ФО-06, ДАК 1 246,389, ДРР 677,714.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="45" customHeight="1">
+          <t>«По плану за период» каждого кредита = план сентября в ФО-06 (план на 01.10.2026, правок плана сентября после 30.09.2026 нет); ИТОГО 1 962,365 = сентябрь ИТОГО ФО-06, ДАК 1 284,651, ДРР 677,714.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="75" customHeight="1">
       <c r="A37" s="41" t="inlineStr">
         <is>
           <t>3.</t>
@@ -3218,11 +3309,11 @@
       </c>
       <c r="B37" s="42" t="inlineStr">
         <is>
-          <t>«Погашено — всего» = платежи кредита за сентябрь в ФО-04; ИТОГО 1 668,438 = ИТОГО ФО-04 1 667,910 + курсовая разница платежа КЗ-11 0,528 (5,275 тыс. USD по 87,50000 = 461,563 против 461,035 по курсу 87,40 на день платежа 05.09.2026).</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="60" customHeight="1">
+          <t>«Погашено — всего» = платежи кредита за сентябрь в ФО-04, у валютных — по курсу на 30.09.2026; ИТОГО 1 706,699 = ИТОГО ФО-04 1 706,077 + курсовая разница платежа КЗ-11 0,528 (5,275 тыс. USD по 87,50000 = 461,563 против 461,035 по курсу 87,40 на день платежа 05.09.2026) + курсовая разница платежа КЗ-25 0,094 (376,96 EUR по 101,50000 = 38,261 против 38,167 по курсу 101,25 на день платежа 21.09.2026).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="75" customHeight="1">
       <c r="A38" s="41" t="inlineStr">
         <is>
           <t>4.</t>
@@ -3230,7 +3321,7 @@
       </c>
       <c r="B38" s="42" t="inlineStr">
         <is>
-          <t>«По графику за период» = «По графику за период» ФО-05 за сентябрь: у кредитов без просрочки — платёж сентября (КЗ-01 170,625 и 112,500; КЗ-15 — 270,000 из погашенных 520,000, остальное — досрочно), у кредитов с просрочкой — платёж сентября графика (КЗ-02 178,500, КЗ-04 230,000, КЗ-05 68,571 — весь долг в суде, в график входит).</t>
+          <t>«По графику за период» = «По графику за период» ФО-05 за сентябрь: у кредитов без просрочки — платёж сентября (КЗ-01 170,625 и 112,500; КЗ-15 — 270,000 из погашенных 520,000, остальное — досрочно), у кредитов с просрочкой — платёж сентября графика (КЗ-02 178,500, КЗ-04 230,000, КЗ-05 68,571 — весь долг в суде, в график входит); ИТОГО 3 159,108 = «По графику за период» ФО-05 за сентябрь.</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3333,7 @@
       </c>
       <c r="B39" s="42" t="inlineStr">
         <is>
-          <t>Исполнение — по суммам строки, не среднее процентов: ДАК 809,688 ÷ 1 246,389 = 65,0 %; ДРР 799,583 ÷ 677,714 = 118,0 %; Асанов А. К. 348,125 ÷ 784,827 = 44,4 %; Бекова Н. С. 100,0 %; Жумабаев Р. С. 72,083 ÷ 95,750 = 75,3 %; Осмонов Б. Т. 611,250 ÷ 465,714 = 131,2 %; Токтогулова Г. А. 116,250 ÷ 116,250 = 100,0 %.</t>
+          <t>Исполнение — по суммам строки, не среднее процентов: ДАК 847,949 ÷ 1 284,651 = 66,0 %; ДРР 799,583 ÷ 677,714 = 118,0 %; Асанов А. К. 348,125 ÷ 784,827 = 44,4 %; Бекова Н. С. 499,824 ÷ 499,824 = 100,0 %; Жумабаев Р. С. 72,083 ÷ 95,750 = 75,3 %; Осмонов Б. Т. 611,250 ÷ 465,714 = 131,2 %; Токтогулова Г. А. 116,250 ÷ 116,250 = 100,0 %.</t>
         </is>
       </c>
     </row>
@@ -3294,7 +3385,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="60" customHeight="1">
+    <row r="44" ht="105" customHeight="1">
       <c r="A44" s="41" t="inlineStr">
         <is>
           <t>10.</t>
@@ -3302,7 +3393,7 @@
       </c>
       <c r="B44" s="42" t="inlineStr">
         <is>
-          <t>Валютные — по курсу на 30.09.2026: КЗ-11 по графику, план и погашено по 5,275 тыс. USD = 461,563, исполнение 100,0 %; КЗ-22 план 2,907 тыс. EUR = 295,027, по графику 3,387 тыс. EUR = 343,747, погашений нет; КЗ-21 № 19-3/061 по графику 3,757 тыс. USD = 328,750; КЗ-23 2,117 тыс. USD = 185,208. Строка «в тыс. USD/EUR» под кредитом, в итоги не входит.</t>
+          <t>Валютные — по курсу на 30.09.2026: КЗ-11 по графику, план и погашено по 5,275 тыс. USD = 461,563, исполнение 100,0 %; КЗ-25 № 21-9/040 — платёж 20.09.2026 (воскресенье, срок 21.09.2026), только проценты: по графику, план и погашено 21.09.2026 по 376,96 EUR = 38,261, исполнение 100,0 %, под Бековой Н. С. «Ала-Арча Энерго» перед «Кут-Мүлк» (недобор 0,00 у обоих — по алфавиту); КЗ-22 план 2,907 тыс. EUR = 295,027, по графику 3,387 тыс. EUR = 343,747, погашений нет; КЗ-21 № 19-3/061 по графику 3,757 тыс. USD = 328,750; КЗ-23 2,117 тыс. USD = 185,208. Строка «в тыс. USD/EUR» под кредитом, в итоги не входит.</t>
         </is>
       </c>
     </row>
